--- a/results/sankey/Basic_example_zorro_1_BS0006.xlsx
+++ b/results/sankey/Basic_example_zorro_1_BS0006.xlsx
@@ -426,13 +426,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z78"/>
+  <dimension ref="A1:Z130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
@@ -1791,6 +1791,942 @@
         <v/>
       </c>
     </row>
+    <row r="79">
+      <c r="A79">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A74")</f>
+        <v/>
+      </c>
+      <c r="B79">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B74")</f>
+        <v/>
+      </c>
+      <c r="C79">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C74")</f>
+        <v/>
+      </c>
+      <c r="D79">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D74")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A75")</f>
+        <v/>
+      </c>
+      <c r="B80">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B75")</f>
+        <v/>
+      </c>
+      <c r="C80">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C75")</f>
+        <v/>
+      </c>
+      <c r="D80">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D75")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A76")</f>
+        <v/>
+      </c>
+      <c r="B81">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B76")</f>
+        <v/>
+      </c>
+      <c r="C81">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C76")</f>
+        <v/>
+      </c>
+      <c r="D81">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D76")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A77")</f>
+        <v/>
+      </c>
+      <c r="B82">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B77")</f>
+        <v/>
+      </c>
+      <c r="C82">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C77")</f>
+        <v/>
+      </c>
+      <c r="D82">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D77")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A78")</f>
+        <v/>
+      </c>
+      <c r="B83">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B78")</f>
+        <v/>
+      </c>
+      <c r="C83">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C78")</f>
+        <v/>
+      </c>
+      <c r="D83">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D78")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A79")</f>
+        <v/>
+      </c>
+      <c r="B84">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B79")</f>
+        <v/>
+      </c>
+      <c r="C84">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C79")</f>
+        <v/>
+      </c>
+      <c r="D84">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D79")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A80")</f>
+        <v/>
+      </c>
+      <c r="B85">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B80")</f>
+        <v/>
+      </c>
+      <c r="C85">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C80")</f>
+        <v/>
+      </c>
+      <c r="D85">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D80")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A81")</f>
+        <v/>
+      </c>
+      <c r="B86">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B81")</f>
+        <v/>
+      </c>
+      <c r="C86">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C81")</f>
+        <v/>
+      </c>
+      <c r="D86">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D81")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A82")</f>
+        <v/>
+      </c>
+      <c r="B87">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B82")</f>
+        <v/>
+      </c>
+      <c r="C87">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C82")</f>
+        <v/>
+      </c>
+      <c r="D87">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D82")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A83")</f>
+        <v/>
+      </c>
+      <c r="B88">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B83")</f>
+        <v/>
+      </c>
+      <c r="C88">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C83")</f>
+        <v/>
+      </c>
+      <c r="D88">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D83")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A84")</f>
+        <v/>
+      </c>
+      <c r="B89">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B84")</f>
+        <v/>
+      </c>
+      <c r="C89">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C84")</f>
+        <v/>
+      </c>
+      <c r="D89">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D84")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A85")</f>
+        <v/>
+      </c>
+      <c r="B90">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B85")</f>
+        <v/>
+      </c>
+      <c r="C90">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C85")</f>
+        <v/>
+      </c>
+      <c r="D90">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D85")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A86")</f>
+        <v/>
+      </c>
+      <c r="B91">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B86")</f>
+        <v/>
+      </c>
+      <c r="C91">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C86")</f>
+        <v/>
+      </c>
+      <c r="D91">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D86")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A87")</f>
+        <v/>
+      </c>
+      <c r="B92">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B87")</f>
+        <v/>
+      </c>
+      <c r="C92">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C87")</f>
+        <v/>
+      </c>
+      <c r="D92">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D87")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A88")</f>
+        <v/>
+      </c>
+      <c r="B93">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B88")</f>
+        <v/>
+      </c>
+      <c r="C93">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C88")</f>
+        <v/>
+      </c>
+      <c r="D93">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D88")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A89")</f>
+        <v/>
+      </c>
+      <c r="B94">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B89")</f>
+        <v/>
+      </c>
+      <c r="C94">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C89")</f>
+        <v/>
+      </c>
+      <c r="D94">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D89")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A90")</f>
+        <v/>
+      </c>
+      <c r="B95">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B90")</f>
+        <v/>
+      </c>
+      <c r="C95">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C90")</f>
+        <v/>
+      </c>
+      <c r="D95">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D90")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A91")</f>
+        <v/>
+      </c>
+      <c r="B96">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B91")</f>
+        <v/>
+      </c>
+      <c r="C96">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C91")</f>
+        <v/>
+      </c>
+      <c r="D96">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D91")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A92")</f>
+        <v/>
+      </c>
+      <c r="B97">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B92")</f>
+        <v/>
+      </c>
+      <c r="C97">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C92")</f>
+        <v/>
+      </c>
+      <c r="D97">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D92")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A93")</f>
+        <v/>
+      </c>
+      <c r="B98">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B93")</f>
+        <v/>
+      </c>
+      <c r="C98">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C93")</f>
+        <v/>
+      </c>
+      <c r="D98">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D93")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A94")</f>
+        <v/>
+      </c>
+      <c r="B99">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B94")</f>
+        <v/>
+      </c>
+      <c r="C99">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C94")</f>
+        <v/>
+      </c>
+      <c r="D99">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D94")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A95")</f>
+        <v/>
+      </c>
+      <c r="B100">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B95")</f>
+        <v/>
+      </c>
+      <c r="C100">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C95")</f>
+        <v/>
+      </c>
+      <c r="D100">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D95")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A96")</f>
+        <v/>
+      </c>
+      <c r="B101">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B96")</f>
+        <v/>
+      </c>
+      <c r="C101">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C96")</f>
+        <v/>
+      </c>
+      <c r="D101">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D96")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A97")</f>
+        <v/>
+      </c>
+      <c r="B102">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B97")</f>
+        <v/>
+      </c>
+      <c r="C102">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C97")</f>
+        <v/>
+      </c>
+      <c r="D102">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D97")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A98")</f>
+        <v/>
+      </c>
+      <c r="B103">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B98")</f>
+        <v/>
+      </c>
+      <c r="C103">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C98")</f>
+        <v/>
+      </c>
+      <c r="D103">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D98")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A99")</f>
+        <v/>
+      </c>
+      <c r="B104">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B99")</f>
+        <v/>
+      </c>
+      <c r="C104">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C99")</f>
+        <v/>
+      </c>
+      <c r="D104">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D99")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A100")</f>
+        <v/>
+      </c>
+      <c r="B105">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B100")</f>
+        <v/>
+      </c>
+      <c r="C105">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C100")</f>
+        <v/>
+      </c>
+      <c r="D105">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D100")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A101")</f>
+        <v/>
+      </c>
+      <c r="B106">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B101")</f>
+        <v/>
+      </c>
+      <c r="C106">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C101")</f>
+        <v/>
+      </c>
+      <c r="D106">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D101")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A102")</f>
+        <v/>
+      </c>
+      <c r="B107">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B102")</f>
+        <v/>
+      </c>
+      <c r="C107">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C102")</f>
+        <v/>
+      </c>
+      <c r="D107">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D102")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A103")</f>
+        <v/>
+      </c>
+      <c r="B108">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B103")</f>
+        <v/>
+      </c>
+      <c r="C108">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C103")</f>
+        <v/>
+      </c>
+      <c r="D108">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D103")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A104")</f>
+        <v/>
+      </c>
+      <c r="B109">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B104")</f>
+        <v/>
+      </c>
+      <c r="C109">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C104")</f>
+        <v/>
+      </c>
+      <c r="D109">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D104")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A105")</f>
+        <v/>
+      </c>
+      <c r="B110">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B105")</f>
+        <v/>
+      </c>
+      <c r="C110">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C105")</f>
+        <v/>
+      </c>
+      <c r="D110">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D105")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A106")</f>
+        <v/>
+      </c>
+      <c r="B111">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B106")</f>
+        <v/>
+      </c>
+      <c r="C111">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C106")</f>
+        <v/>
+      </c>
+      <c r="D111">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D106")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A107")</f>
+        <v/>
+      </c>
+      <c r="B112">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B107")</f>
+        <v/>
+      </c>
+      <c r="C112">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C107")</f>
+        <v/>
+      </c>
+      <c r="D112">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D107")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A108")</f>
+        <v/>
+      </c>
+      <c r="B113">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B108")</f>
+        <v/>
+      </c>
+      <c r="C113">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C108")</f>
+        <v/>
+      </c>
+      <c r="D113">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D108")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A109")</f>
+        <v/>
+      </c>
+      <c r="B114">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B109")</f>
+        <v/>
+      </c>
+      <c r="C114">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C109")</f>
+        <v/>
+      </c>
+      <c r="D114">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D109")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A110")</f>
+        <v/>
+      </c>
+      <c r="B115">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B110")</f>
+        <v/>
+      </c>
+      <c r="C115">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C110")</f>
+        <v/>
+      </c>
+      <c r="D115">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D110")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A111")</f>
+        <v/>
+      </c>
+      <c r="B116">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B111")</f>
+        <v/>
+      </c>
+      <c r="C116">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C111")</f>
+        <v/>
+      </c>
+      <c r="D116">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D111")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A112")</f>
+        <v/>
+      </c>
+      <c r="B117">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B112")</f>
+        <v/>
+      </c>
+      <c r="C117">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C112")</f>
+        <v/>
+      </c>
+      <c r="D117">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D112")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A113")</f>
+        <v/>
+      </c>
+      <c r="B118">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B113")</f>
+        <v/>
+      </c>
+      <c r="C118">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C113")</f>
+        <v/>
+      </c>
+      <c r="D118">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D113")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A114")</f>
+        <v/>
+      </c>
+      <c r="B119">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B114")</f>
+        <v/>
+      </c>
+      <c r="C119">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C114")</f>
+        <v/>
+      </c>
+      <c r="D119">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D114")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A115")</f>
+        <v/>
+      </c>
+      <c r="B120">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B115")</f>
+        <v/>
+      </c>
+      <c r="C120">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C115")</f>
+        <v/>
+      </c>
+      <c r="D120">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D115")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A116")</f>
+        <v/>
+      </c>
+      <c r="B121">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B116")</f>
+        <v/>
+      </c>
+      <c r="C121">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C116")</f>
+        <v/>
+      </c>
+      <c r="D121">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D116")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A117")</f>
+        <v/>
+      </c>
+      <c r="B122">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B117")</f>
+        <v/>
+      </c>
+      <c r="C122">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C117")</f>
+        <v/>
+      </c>
+      <c r="D122">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D117")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A118")</f>
+        <v/>
+      </c>
+      <c r="B123">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B118")</f>
+        <v/>
+      </c>
+      <c r="C123">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C118")</f>
+        <v/>
+      </c>
+      <c r="D123">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D118")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A119")</f>
+        <v/>
+      </c>
+      <c r="B124">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B119")</f>
+        <v/>
+      </c>
+      <c r="C124">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C119")</f>
+        <v/>
+      </c>
+      <c r="D124">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D119")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A120")</f>
+        <v/>
+      </c>
+      <c r="B125">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B120")</f>
+        <v/>
+      </c>
+      <c r="C125">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C120")</f>
+        <v/>
+      </c>
+      <c r="D125">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D120")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A121")</f>
+        <v/>
+      </c>
+      <c r="B126">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B121")</f>
+        <v/>
+      </c>
+      <c r="C126">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C121")</f>
+        <v/>
+      </c>
+      <c r="D126">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D121")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A122")</f>
+        <v/>
+      </c>
+      <c r="B127">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B122")</f>
+        <v/>
+      </c>
+      <c r="C127">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C122")</f>
+        <v/>
+      </c>
+      <c r="D127">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D122")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A123")</f>
+        <v/>
+      </c>
+      <c r="B128">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B123")</f>
+        <v/>
+      </c>
+      <c r="C128">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C123")</f>
+        <v/>
+      </c>
+      <c r="D128">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D123")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A124")</f>
+        <v/>
+      </c>
+      <c r="B129">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B124")</f>
+        <v/>
+      </c>
+      <c r="C129">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C124")</f>
+        <v/>
+      </c>
+      <c r="D129">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D124")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A125")</f>
+        <v/>
+      </c>
+      <c r="B130">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B125")</f>
+        <v/>
+      </c>
+      <c r="C130">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C125")</f>
+        <v/>
+      </c>
+      <c r="D130">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D125")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -1807,7 +2743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1848,12 +2784,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>AW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ElectricityIn</t>
+          <t>Recovery heat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1862,18 +2798,18 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>691127.9171590982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BioTransformer</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Solidfuel</t>
+          <t>ElectricityIn</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1882,23 +2818,23 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2113344.934501374</v>
+        <v>691127.9171590982</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BioWood</t>
+          <t>BioTransformer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BioTransformer</t>
+          <t>Solidfuel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>outgoing</t>
+          <t>incoming</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1913,7 +2849,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Biomasse_elec_heat</t>
+          <t>BioTransformer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1922,7 +2858,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>935832.0863227621</v>
+        <v>2113344.934501374</v>
       </c>
     </row>
     <row r="7">
@@ -1933,7 +2869,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BtL_Holz</t>
+          <t>Biomasse_elec</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1942,38 +2878,38 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3508545.0001759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Biogas_feedin_existing</t>
+          <t>BioWood</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Biomasse_elec_heat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1098777.135435311</v>
+        <v>935832.0863227621</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biomass</t>
+          <t>BioWood</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Biogas_feedin_existing</t>
+          <t>Biomasse_heat</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1982,18 +2918,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1248610.38117649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Biomass</t>
+          <t>BioWood</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BtL_substrat</t>
+          <t>BtL_Holz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2002,13 +2938,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2633637.127822987</v>
+        <v>3508545.0001759</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Biomasse_elec_heat</t>
+          <t>Biogas- BHKW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2022,13 +2958,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>533424.2892039743</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Biomasse_elec_heat</t>
+          <t>Biogas- BHKW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2042,18 +2978,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>308824.5884865116</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BtL_Holz</t>
+          <t>Biogas_feedin_existing</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Oil_fuel</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,18 +2998,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1613930.700080913</v>
+        <v>1098777.135435311</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BtL_substrat</t>
+          <t>Biogas_feedin_new</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Oil_fuel</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2082,18 +3018,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1580182.276693792</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>District heating</t>
+          <t>Biomass</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Heat storage_dist_heat</t>
+          <t>Biogas- BHKW</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2102,18 +3038,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>406546.9555798536</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>District heating</t>
+          <t>Biomass</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Heat storage_seasonal</t>
+          <t>Biogas_feedin_existing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2122,18 +3058,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1237558.871866925</v>
+        <v>1248610.38117649</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>District heating</t>
+          <t>Biomass</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Heat_demand_total</t>
+          <t>Biogas_feedin_new</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2142,18 +3078,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2918198.990133206</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>District heating</t>
+          <t>Biomass</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>excess_b_distheat</t>
+          <t>BtL_substrat</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2162,158 +3098,158 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>641771.8793898962</v>
+        <v>2633637.127822987</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Electric boiler</t>
+          <t>Biomass</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>District heating</t>
+          <t>excess_b_bio</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2369849.308292164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Biomasse_elec</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>ElectricityIn</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>outgoing</t>
+          <t>incoming</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>743148.2980205361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ElectricityIn</t>
+          <t>Biomasse_elec_heat</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Natrium_Battery</t>
+          <t>District heating</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>outgoing</t>
+          <t>incoming</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1703717.505273704</v>
+        <v>533424.2892039743</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Biomasse_elec_heat</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>ElectricityIn</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Netzverluste</t>
-        </is>
-      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>outgoing</t>
+          <t>incoming</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>39388992.6139124</v>
+        <v>308824.5884865116</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ElectricityIn</t>
+          <t>Biomasse_heat</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pumped_hydro_storage_bestand</t>
+          <t>District heating</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>outgoing</t>
+          <t>incoming</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>712895.9424866366</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ElectricityOut</t>
+          <t>BtL_Holz</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Electric boiler</t>
+          <t>Oil_fuel</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>outgoing</t>
+          <t>incoming</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2393787.180093094</v>
+        <v>1613930.700080913</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ElectricityOut</t>
+          <t>BtL_substrat</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Electricity_demand_Rechenzentren</t>
+          <t>Oil_fuel</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>outgoing</t>
+          <t>incoming</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3599589.04109589</v>
+        <v>1580182.276693792</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ElectricityOut</t>
+          <t>District heating</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Electricity_demand_total</t>
+          <t>Heat storage_dist_heat</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2322,18 +3258,18 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>19386565.03091698</v>
+        <v>406546.9555798536</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ElectricityOut</t>
+          <t>District heating</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Electrolysis</t>
+          <t>Heat storage_seasonal</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2342,18 +3278,18 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>5776960.54239567</v>
+        <v>1237558.871866925</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ElectricityOut</t>
+          <t>District heating</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Export_Electricity</t>
+          <t>Heat_demand_total</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2362,18 +3298,18 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5500703.701841522</v>
+        <v>2918198.990133206</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ElectricityOut</t>
+          <t>District heating</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Heatpump_air</t>
+          <t>excess_b_distheat</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2382,38 +3318,38 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>175782.0321420208</v>
+        <v>641771.8793898962</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ElectricityOut</t>
+          <t>Electric boiler</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Preheater- Electric boiler</t>
+          <t>District heating</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>outgoing</t>
+          <t>incoming</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>629.2675055124204</v>
+        <v>2369849.308292164</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ElectricityOut</t>
+          <t>ElectricityIn</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PtL</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2422,13 +3358,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>585526.1872250665</v>
+        <v>743148.2980205361</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Electricity_Hös</t>
+          <t>ElectricityIn</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2442,38 +3378,38 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5500703.701841135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Electrolysis</t>
+          <t>ElectricityIn</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Li-Ion_Battery</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4043872.379676969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>ElectricityIn</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gas_demand_total</t>
+          <t>Natrium_Battery</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2482,18 +3418,18 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2171329.883786918</v>
+        <v>1703717.505273704</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>ElectricityIn</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gas_storage</t>
+          <t>Netzverluste</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2502,18 +3438,18 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>355584.6298967428</v>
+        <v>39388992.6139124</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>ElectricityIn</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Material_demand_Gas</t>
+          <t>Pumped_hydro_storage_bestand</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2522,138 +3458,138 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9275.865990296803</v>
+        <v>712895.9424866366</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Gas_storage</t>
+          <t>ElectricityIn</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Red-OX_Battery</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>337805.3984018926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>H2_storage</t>
+          <t>ElectricityOut</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Electric boiler</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1689611.309831562</v>
+        <v>2393787.180093094</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Heat storage_dist_heat</t>
+          <t>ElectricityOut</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>District heating</t>
+          <t>Electricity_demand_Rechenzentren</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>390732.752140057</v>
+        <v>3599589.04109589</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Heat storage_seasonal</t>
+          <t>ElectricityOut</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Preheater</t>
+          <t>Electricity_demand_total</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1145855.917502219</v>
+        <v>19386565.03091698</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Heatpump_air</t>
+          <t>ElectricityOut</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>District heating</t>
+          <t>Electrolysis</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>763585.1623259563</v>
+        <v>5776960.54239567</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Hydro power plant</t>
+          <t>ElectricityOut</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ElectricityIn</t>
+          <t>Export_Electricity</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>195270.86</v>
+        <v>5500703.701841522</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>ElectricityOut</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H2_storage</t>
+          <t>Heatpump_air</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2662,18 +3598,18 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1877345.89981285</v>
+        <v>175782.0321420208</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>ElectricityOut</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hydrogen_demand_total</t>
+          <t>Heatpump_recovery_heat</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2682,18 +3618,18 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1390108.146468243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>ElectricityOut</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Methanisation</t>
+          <t>Heatpump_water</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2702,18 +3638,18 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1221786.495374172</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>ElectricityOut</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PtL</t>
+          <t>Preheater- Electric boiler</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2722,118 +3658,118 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1244243.147853266</v>
+        <v>629.2675055124204</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Hös&lt;-&gt;HS</t>
+          <t>ElectricityOut</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ElectricityIn</t>
+          <t>Preheater- WP</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>5500703.701841135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Import_Electricity</t>
+          <t>ElectricityOut</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Electricity_Hös</t>
+          <t>PtL</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>5500703.701841135</v>
+        <v>585526.1872250665</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Import_Wood</t>
+          <t>ElectricityOut</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BioWood</t>
+          <t>excess_b_el</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>6557722.021000034</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Import_solid_fuel</t>
+          <t>Electricity_Hös</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Biomass</t>
+          <t>Hös&lt;-&gt;HS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3882247.508999479</v>
+        <v>5500703.701841135</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Methanisation</t>
+          <t>Electricity_Hös</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Pumped_hydro_technology</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1099607.845836754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Natrium_Battery</t>
+          <t>Electrolysis</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ElectricityIn</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2842,58 +3778,58 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1533345.754746334</v>
+        <v>4043872.379676969</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Netzverluste</t>
+          <t>Environmental heat</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ElectricityOut</t>
+          <t>Heatpump_water</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>37419542.98321678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Oil_fuel</t>
+          <t>Fuelcell</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Material_demand_Oil</t>
+          <t>ElectricityIn</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>outgoing</t>
+          <t>incoming</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>836815.6246960615</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Oil_fuel</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Oil &amp; fuel_demand_total</t>
+          <t>Gas_demand_total</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2902,113 +3838,113 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3455158.953126198</v>
+        <v>2171329.883786918</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PV_open_east</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ElectricityIn</t>
+          <t>Gas_storage</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2588177.221866487</v>
+        <v>355584.6298967428</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PV_open_middle</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ElectricityIn</t>
+          <t>GuD</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4213199.797083519</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PV_open_north</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ElectricityIn</t>
+          <t>Material_demand_Gas</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3255380.519636255</v>
+        <v>9275.865990296803</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PV_open_swest</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ElectricityIn</t>
+          <t>excess_b_gas</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2545999.68166156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Preheater</t>
+          <t>Gas_storage</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Preheater- Electric boiler</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>outgoing</t>
+          <t>incoming</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1145855.917502219</v>
+        <v>337805.3984018926</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Preheater- Electric boiler</t>
+          <t>GuD</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3022,18 +3958,18 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1146485.185007731</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PtL</t>
+          <t>GuD</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Oil_fuel</t>
+          <t>ElectricityIn</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3042,18 +3978,18 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1097861.601047</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Pumped_hydro_storage_bestand</t>
+          <t>H2_storage</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ElectricityIn</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3062,58 +3998,58 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>609526.0308260742</v>
+        <v>1689611.309831562</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Solidfuel</t>
+          <t>Heat storage_dist_heat</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Biomass_demand_total</t>
+          <t>District heating</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>outgoing</t>
+          <t>incoming</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2012919.487402344</v>
+        <v>390732.752140057</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Solidfuel</t>
+          <t>Heat storage_seasonal</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Material_demand_Biomasse</t>
+          <t>Preheater</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>outgoing</t>
+          <t>incoming</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>100425.4470990297</v>
+        <v>1145855.917502219</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Umgebungsluft</t>
+          <t>Heatpump_air</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Umgebungsluftbus</t>
+          <t>District heating</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3122,38 +4058,38 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>587803.1301839355</v>
+        <v>763585.1623259563</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Umgebungsluftbus</t>
+          <t>Heatpump_recovery_heat</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Heatpump_air</t>
+          <t>District heating</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>outgoing</t>
+          <t>incoming</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>587803.1301839355</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Wind_east</t>
+          <t>Heatpump_water</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ElectricityIn</t>
+          <t>District heating</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3162,13 +4098,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2133986.584684227</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Wind_middle</t>
+          <t>Hydro power plant</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3182,86 +4118,1126 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5521819.839000258</v>
+        <v>195270.86</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Wind_north</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ElectricityIn</t>
+          <t>Export_Hydrogen</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>7634239.902191051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Wind_swest</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ElectricityIn</t>
+          <t>Fuelcell</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>5817151.960510769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PV_total</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ElectricityIN</t>
+          <t>H2_storage</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12602757.22024782</v>
+        <v>1877345.89981285</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Hydrogen_demand_total</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1390108.146468243</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Methanisation</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1221786.495374172</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PtL</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1244243.147853266</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>excess_b_H2</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Hös&lt;-&gt;HS</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>5500703.701841135</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Hös&lt;-&gt;HS</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Electricity_Hös</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Import_Electricity</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Electricity_Hös</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>5500703.701841135</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Import_Gas</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Import_Hydrogen</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Import_Oil</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Oil_fuel</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Import_Synthetic_fuel</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Oil_fuel</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Import_Wood</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>BioWood</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>6557722.021000034</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Import_solid_fuel</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Biomass</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>3882247.508999479</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Li-Ion_Battery</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Methanisation</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1099607.845836754</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Natrium_Battery</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1533345.754746334</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Netzverluste</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ElectricityOut</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>37419542.98321678</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Oil_fuel</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Material_demand_Oil</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>836815.6246960615</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Oil_fuel</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Oil &amp; fuel_demand_total</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>3455158.953126198</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Oil_fuel</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>excess_b_oil_fuel</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>PV_open_east</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>2588177.221866487</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>PV_open_middle</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>4213199.797083519</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>PV_open_north</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>3255380.519636255</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>PV_open_swest</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>2545999.68166156</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>PV_rooftop_east</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>PV_rooftop_middle</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>PV_rooftop_north</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>PV_rooftop_swest</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Preheater</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Preheater- Electric boiler</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1145855.917502219</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Preheater</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Preheater- WP</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Preheater- Electric boiler</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>District heating</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1146485.185007731</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Preheater- WP</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>District heating</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>PtL</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Oil_fuel</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1097861.601047</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Pumped-Hydro</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Pumped_hydro_storage</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Pumped-Hydro</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Pumped_hydro_technology</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Pumped_hydro_storage</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Pumped-Hydro</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Pumped_hydro_storage_bestand</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>609526.0308260742</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Pumped_hydro_technology</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Electricity_Hös</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Pumped_hydro_technology</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Pumped-Hydro</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Recovery heat</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Heatpump_recovery_heat</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Red-OX_Battery</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>District heating</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Solidfuel</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Biomass_demand_total</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>2012919.487402344</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Solidfuel</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Material_demand_Biomasse</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>100425.4470990297</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>UW</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Environmental heat</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Umgebungsluft</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Umgebungsluftbus</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>587803.1301839355</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Umgebungsluftbus</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Heatpump_air</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>587803.1301839355</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Wind_east</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>2133986.584684227</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Wind_middle</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>5521819.839000258</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Wind_north</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>7634239.902191051</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Wind_swest</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>5817151.960510769</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>PV_total</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ElectricityIN</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>12602757.22024782</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
           <t>Wind_total</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>ElectricityIN</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>incoming</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
         <v>21107198.2863863</v>
       </c>
     </row>

--- a/results/sankey/Basic_example_zorro_1_BS0006.xlsx
+++ b/results/sankey/Basic_example_zorro_1_BS0006.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2045_BS0006_final_26_02_26" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2020_BS0006_final_26_02_26" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z130"/>
+  <dimension ref="A1:Z131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -465,7 +465,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>2045_BS0006_final_26_02_26</t>
+          <t>2020_BS0006_final_26_02_26</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2045_BS0006_final_26_02_26</t>
+          <t>2020_BS0006_final_26_02_26</t>
         </is>
       </c>
     </row>
@@ -2724,6 +2724,24 @@
       </c>
       <c r="D130">
         <f>INDIRECT("'"&amp;$B$3&amp;"'!D125")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!A126")</f>
+        <v/>
+      </c>
+      <c r="B131">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!B126")</f>
+        <v/>
+      </c>
+      <c r="C131">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!C126")</f>
+        <v/>
+      </c>
+      <c r="D131">
+        <f>INDIRECT("'"&amp;$B$3&amp;"'!D126")</f>
         <v/>
       </c>
     </row>
@@ -2743,19 +2761,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D125"/>
+  <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>2045_BS0006_final_26_02_26</t>
+          <t>2020_BS0006_final_26_02_26</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2836,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>691127.9171590982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2838,7 +2856,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2113344.934501374</v>
+        <v>3010267.207475102</v>
       </c>
     </row>
     <row r="6">
@@ -2858,7 +2876,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2113344.934501374</v>
+        <v>3010267.207475102</v>
       </c>
     </row>
     <row r="7">
@@ -2898,7 +2916,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>935832.0863227621</v>
+        <v>3547454.813524587</v>
       </c>
     </row>
     <row r="9">
@@ -2938,7 +2956,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3508545.0001759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2958,7 +2976,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>148.5000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2978,7 +2996,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>127.7100000000001</v>
       </c>
     </row>
     <row r="13">
@@ -2998,7 +3016,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1098777.135435311</v>
+        <v>2601423</v>
       </c>
     </row>
     <row r="14">
@@ -3018,7 +3036,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>814693.4479202805</v>
       </c>
     </row>
     <row r="15">
@@ -3038,7 +3056,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>297.0000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -3058,7 +3076,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1248610.38117649</v>
+        <v>2956162.5</v>
       </c>
     </row>
     <row r="17">
@@ -3078,7 +3096,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>925788.0090003184</v>
       </c>
     </row>
     <row r="18">
@@ -3098,7 +3116,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2633637.127822987</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3158,7 +3176,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>533424.2892039743</v>
+        <v>2022049.243709015</v>
       </c>
     </row>
     <row r="22">
@@ -3178,7 +3196,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>308824.5884865116</v>
+        <v>1170660.088463114</v>
       </c>
     </row>
     <row r="23">
@@ -3218,7 +3236,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1613930.700080913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3238,7 +3256,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1580182.276693792</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3258,7 +3276,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>406546.9555798536</v>
+        <v>444177.6609793192</v>
       </c>
     </row>
     <row r="27">
@@ -3278,7 +3296,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1237558.871866925</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -3298,7 +3316,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2918198.990133206</v>
+        <v>3549381.07446548</v>
       </c>
     </row>
     <row r="29">
@@ -3318,7 +3336,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>641771.8793898962</v>
+        <v>2768764.198485626</v>
       </c>
     </row>
     <row r="30">
@@ -3338,7 +3356,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2369849.308292164</v>
+        <v>2186404.919296104</v>
       </c>
     </row>
     <row r="31">
@@ -3358,7 +3376,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>743148.2980205361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3378,7 +3396,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>571897.7517342005</v>
       </c>
     </row>
     <row r="33">
@@ -3418,7 +3436,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1703717.505273704</v>
+        <v>1483283.965226344</v>
       </c>
     </row>
     <row r="35">
@@ -3438,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>39388992.6139124</v>
+        <v>19761772.95001874</v>
       </c>
     </row>
     <row r="36">
@@ -3458,7 +3476,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>712895.9424866366</v>
+        <v>897690.1844708072</v>
       </c>
     </row>
     <row r="37">
@@ -3498,7 +3516,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2393787.180093094</v>
+        <v>2208489.817470812</v>
       </c>
     </row>
     <row r="39">
@@ -3518,7 +3536,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3599589.04109589</v>
+        <v>719917.8082191778</v>
       </c>
     </row>
     <row r="40">
@@ -3538,7 +3556,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>19386565.03091698</v>
+        <v>11381744.02152988</v>
       </c>
     </row>
     <row r="41">
@@ -3558,7 +3576,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>5776960.54239567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3578,7 +3596,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>5500703.701841522</v>
+        <v>4141993.443369079</v>
       </c>
     </row>
     <row r="43">
@@ -3598,7 +3616,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>175782.0321420208</v>
+        <v>286502.3902282274</v>
       </c>
     </row>
     <row r="44">
@@ -3658,7 +3676,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>629.2675055124204</v>
+        <v>4.923128982446657e-14</v>
       </c>
     </row>
     <row r="47">
@@ -3698,7 +3716,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>585526.1872250665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3718,7 +3736,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>35036.82170062813</v>
       </c>
     </row>
     <row r="50">
@@ -3738,7 +3756,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>5500703.701841135</v>
+        <v>1034614.184794915</v>
       </c>
     </row>
     <row r="51">
@@ -3758,7 +3776,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>610678.5948680196</v>
       </c>
     </row>
     <row r="52">
@@ -3778,7 +3796,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4043872.379676969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3818,7 +3836,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1.875832822406667e-13</v>
       </c>
     </row>
     <row r="55">
@@ -3838,7 +3856,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2171329.883786918</v>
+        <v>16411334.92810838</v>
       </c>
     </row>
     <row r="56">
@@ -3858,7 +3876,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>355584.6298967428</v>
+        <v>200615.9360522447</v>
       </c>
     </row>
     <row r="57">
@@ -3878,7 +3896,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>1649852.221694569</v>
       </c>
     </row>
     <row r="58">
@@ -3898,7 +3916,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>9275.865990296803</v>
+        <v>10522.92061621005</v>
       </c>
     </row>
     <row r="59">
@@ -3938,7 +3956,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>337805.3984018926</v>
+        <v>190585.1392496309</v>
       </c>
     </row>
     <row r="61">
@@ -3958,7 +3976,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>659940.8886778275</v>
       </c>
     </row>
     <row r="62">
@@ -3978,7 +3996,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>923917.2441489586</v>
       </c>
     </row>
     <row r="63">
@@ -3998,7 +4016,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1689611.309831562</v>
+        <v>-3.31029321601176e-12</v>
       </c>
     </row>
     <row r="64">
@@ -4018,7 +4036,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>390732.752140057</v>
+        <v>426434.9901923353</v>
       </c>
     </row>
     <row r="65">
@@ -4038,7 +4056,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1145855.917502219</v>
+        <v>1.527819471564373e-12</v>
       </c>
     </row>
     <row r="66">
@@ -4058,7 +4076,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>763585.1623259563</v>
+        <v>1467344.392055145</v>
       </c>
     </row>
     <row r="67">
@@ -4158,7 +4176,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>3.6781035733464e-13</v>
       </c>
     </row>
     <row r="72">
@@ -4178,7 +4196,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1877345.89981285</v>
+        <v>-3.678103573346401e-12</v>
       </c>
     </row>
     <row r="73">
@@ -4198,7 +4216,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1390108.146468243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4218,7 +4236,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1221786.495374172</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4238,7 +4256,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1244243.147853266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4278,7 +4296,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>5500703.701841135</v>
+        <v>1034614.184794915</v>
       </c>
     </row>
     <row r="78">
@@ -4298,7 +4316,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>571897.7517342005</v>
       </c>
     </row>
     <row r="79">
@@ -4318,7 +4336,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5500703.701841135</v>
+        <v>626973.7081153407</v>
       </c>
     </row>
     <row r="80">
@@ -4338,7 +4356,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>14665624.41930149</v>
       </c>
     </row>
     <row r="81">
@@ -4378,7 +4396,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>21023814.95958922</v>
       </c>
     </row>
     <row r="83">
@@ -4418,18 +4436,18 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>6557722.021000034</v>
+        <v>6557722.020999691</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Import_solid_fuel</t>
+          <t>Import_brown_coal</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Biomass</t>
+          <t>Solidfuel</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4438,18 +4456,18 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>3882247.508999479</v>
+        <v>253421.7990997918</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Li-Ion_Battery</t>
+          <t>Import_solid_fuel</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ElectricityIn</t>
+          <t>Biomass</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4458,18 +4476,18 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>3882247.509000318</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Methanisation</t>
+          <t>Li-Ion_Battery</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>ElectricityIn</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4478,18 +4496,18 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1099607.845836754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Natrium_Battery</t>
+          <t>Methanisation</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ElectricityIn</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4498,18 +4516,18 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1533345.754746334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Netzverluste</t>
+          <t>Natrium_Battery</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ElectricityOut</t>
+          <t>ElectricityIn</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4518,27 +4536,27 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>37419542.98321678</v>
+        <v>1334955.568703709</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Oil_fuel</t>
+          <t>Netzverluste</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Material_demand_Oil</t>
+          <t>ElectricityOut</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>outgoing</t>
+          <t>incoming</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>836815.6246960615</v>
+        <v>18773684.30251781</v>
       </c>
     </row>
     <row r="91">
@@ -4549,7 +4567,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Oil &amp; fuel_demand_total</t>
+          <t>Material_demand_Oil</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4558,7 +4576,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>3455158.953126198</v>
+        <v>949317.7670195205</v>
       </c>
     </row>
     <row r="92">
@@ -4569,7 +4587,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>excess_b_oil_fuel</t>
+          <t>Oil &amp; fuel_demand_total</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4578,33 +4596,33 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>20074497.1925697</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PV_open_east</t>
+          <t>Oil_fuel</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ElectricityIn</t>
+          <t>excess_b_oil_fuel</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2588177.221866487</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PV_open_middle</t>
+          <t>PV_open_east</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4618,13 +4636,13 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>4213199.797083519</v>
+        <v>1704504.85316541</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PV_open_north</t>
+          <t>PV_open_middle</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4638,13 +4656,13 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>3255380.519636255</v>
+        <v>2345178.102625134</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PV_open_swest</t>
+          <t>PV_open_north</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4658,13 +4676,13 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2545999.68166156</v>
+        <v>1739481.116700178</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PV_rooftop_east</t>
+          <t>PV_open_swest</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4678,13 +4696,13 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>2350883.360886133</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PV_rooftop_middle</t>
+          <t>PV_rooftop_east</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4704,7 +4722,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PV_rooftop_north</t>
+          <t>PV_rooftop_middle</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4724,7 +4742,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PV_rooftop_swest</t>
+          <t>PV_rooftop_north</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4744,21 +4762,21 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Preheater</t>
+          <t>PV_rooftop_swest</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Preheater- Electric boiler</t>
+          <t>ElectricityIn</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>outgoing</t>
+          <t>incoming</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1145855.917502219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -4769,7 +4787,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Preheater- WP</t>
+          <t>Preheater- Electric boiler</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4778,33 +4796,33 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>1.641506309285989e-12</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Preheater- Electric boiler</t>
+          <t>Preheater</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>District heating</t>
+          <t>Preheater- WP</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1146485.185007731</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Preheater- WP</t>
+          <t>Preheater- Electric boiler</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4818,18 +4836,18 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>1.651716579962401e-12</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PtL</t>
+          <t>Preheater- WP</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Oil_fuel</t>
+          <t>District heating</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4838,23 +4856,23 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1097861.601047</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Pumped-Hydro</t>
+          <t>PtL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Pumped_hydro_storage</t>
+          <t>Oil_fuel</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>outgoing</t>
+          <t>incoming</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4869,7 +4887,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Pumped_hydro_technology</t>
+          <t>Pumped_hydro_storage</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4878,38 +4896,38 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>522130.1986121568</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Pumped_hydro_storage</t>
+          <t>Pumped-Hydro</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Pumped-Hydro</t>
+          <t>Pumped_hydro_technology</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>446421.3198133938</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Pumped_hydro_storage_bestand</t>
+          <t>Pumped_hydro_storage</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ElectricityIn</t>
+          <t>Pumped-Hydro</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4918,18 +4936,18 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>609526.0308260742</v>
+        <v>446421.3198133938</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Pumped_hydro_technology</t>
+          <t>Pumped_hydro_storage_bestand</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Electricity_Hös</t>
+          <t>ElectricityIn</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4938,7 +4956,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>767525.10772254</v>
       </c>
     </row>
     <row r="111">
@@ -4949,7 +4967,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Pumped-Hydro</t>
+          <t>Electricity_Hös</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4958,43 +4976,43 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>446421.3198133938</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Recovery heat</t>
+          <t>Pumped_hydro_technology</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Heatpump_recovery_heat</t>
+          <t>Pumped-Hydro</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>outgoing</t>
+          <t>incoming</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>522130.1986121568</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Red-OX_Battery</t>
+          <t>Recovery heat</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ElectricityIn</t>
+          <t>Heatpump_recovery_heat</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -5004,12 +5022,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>Red-OX_Battery</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>District heating</t>
+          <t>ElectricityIn</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5024,21 +5042,21 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Solidfuel</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Biomass_demand_total</t>
+          <t>District heating</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>outgoing</t>
+          <t>incoming</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2012919.487402344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -5049,7 +5067,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Material_demand_Biomasse</t>
+          <t>Biomass_demand_total</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -5058,38 +5076,38 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>100425.4470990297</v>
+        <v>3149762.284393272</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>UW</t>
+          <t>Solidfuel</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Environmental heat</t>
+          <t>Material_demand_Biomasse</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>113926.722181621</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Umgebungsluft</t>
+          <t>UW</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Umgebungsluftbus</t>
+          <t>Environmental heat</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5098,53 +5116,53 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>587803.1301839355</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
+          <t>Umgebungsluft</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
           <t>Umgebungsluftbus</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Heatpump_air</t>
-        </is>
-      </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>outgoing</t>
+          <t>incoming</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>587803.1301839355</v>
+        <v>1180842.001826</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Wind_east</t>
+          <t>Umgebungsluftbus</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ElectricityIn</t>
+          <t>Heatpump_air</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>incoming</t>
+          <t>outgoing</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>2133986.584684227</v>
+        <v>1180842.001826</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Wind_middle</t>
+          <t>Wind_east</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5158,13 +5176,13 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>5521819.839000258</v>
+        <v>2259218.421832</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Wind_north</t>
+          <t>Wind_middle</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5178,13 +5196,13 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>7634239.902191051</v>
+        <v>2290261.235587</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Wind_swest</t>
+          <t>Wind_north</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5198,18 +5216,18 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>5817151.960510769</v>
+        <v>2298777.447212</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PV_total</t>
+          <t>Wind_swest</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ElectricityIN</t>
+          <t>ElectricityIn</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5218,27 +5236,47 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>12602757.22024782</v>
+        <v>2299269.549609</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
+          <t>PV_total</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>ElectricityIN</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>8140047.433376854</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
           <t>Wind_total</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>ElectricityIN</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>incoming</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>21107198.2863863</v>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>9147526.654239999</v>
       </c>
     </row>
   </sheetData>

--- a/results/sankey/Basic_example_zorro_1_BS0006.xlsx
+++ b/results/sankey/Basic_example_zorro_1_BS0006.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Main" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="2020_BS0006_final_26_02_26" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2045_BS0006_final_26_02_26" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z131"/>
+  <dimension ref="A1:Z130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -469,7 +470,13 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2045_BS0006_final_26_02_26</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2727,28 +2734,10 @@
         <v/>
       </c>
     </row>
-    <row r="131">
-      <c r="A131">
-        <f>INDIRECT("'"&amp;$B$3&amp;"'!A126")</f>
-        <v/>
-      </c>
-      <c r="B131">
-        <f>INDIRECT("'"&amp;$B$3&amp;"'!B126")</f>
-        <v/>
-      </c>
-      <c r="C131">
-        <f>INDIRECT("'"&amp;$B$3&amp;"'!C126")</f>
-        <v/>
-      </c>
-      <c r="D131">
-        <f>INDIRECT("'"&amp;$B$3&amp;"'!D126")</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=Z1:Z1</formula1>
+      <formula1>=Z1:Z2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5282,4 +5271,2513 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D125"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>2045_BS0006_final_26_02_26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>flow_type</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Recovery heat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>691127.9171590982</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BioTransformer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Solidfuel</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2113344.934501374</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BioWood</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BioTransformer</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2113344.934501374</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BioWood</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Biomasse_elec</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BioWood</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Biomasse_elec_heat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>935832.0863227621</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BioWood</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Biomasse_heat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BioWood</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BtL_Holz</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3508545.0001759</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Biogas- BHKW</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>District heating</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Biogas- BHKW</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Biogas_feedin_existing</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1098777.135435311</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Biogas_feedin_new</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Biomass</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Biogas- BHKW</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Biomass</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Biogas_feedin_existing</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1248610.38117649</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Biomass</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Biogas_feedin_new</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Biomass</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BtL_substrat</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2633637.127822987</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Biomass</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>excess_b_bio</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Biomasse_elec</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Biomasse_elec_heat</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>District heating</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>533424.2892039743</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Biomasse_elec_heat</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>308824.5884865116</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Biomasse_heat</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>District heating</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BtL_Holz</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Oil_fuel</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1613930.700080913</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BtL_substrat</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Oil_fuel</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1580182.276693792</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>District heating</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Heat storage_dist_heat</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>406546.9555798536</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>District heating</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Heat storage_seasonal</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1237558.871866925</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>District heating</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Heat_demand_total</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2918198.990133206</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>District heating</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>excess_b_distheat</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>641771.8793898962</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Electric boiler</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>District heating</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2369849.308292164</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>743148.2980205361</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Hös&lt;-&gt;HS</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Li-Ion_Battery</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Natrium_Battery</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1703717.505273704</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Netzverluste</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>39388992.6139124</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pumped_hydro_storage_bestand</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>712895.9424866366</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Red-OX_Battery</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ElectricityOut</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Electric boiler</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2393787.180093094</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ElectricityOut</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Electricity_demand_Rechenzentren</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>3599589.04109589</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ElectricityOut</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Electricity_demand_total</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>19386565.03091698</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ElectricityOut</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Electrolysis</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>5776960.54239567</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ElectricityOut</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Export_Electricity</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>5500703.701841522</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ElectricityOut</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Heatpump_air</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>175782.0321420208</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ElectricityOut</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Heatpump_recovery_heat</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ElectricityOut</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Heatpump_water</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ElectricityOut</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Preheater- Electric boiler</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>629.2675055124204</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ElectricityOut</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Preheater- WP</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ElectricityOut</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>PtL</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>585526.1872250665</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ElectricityOut</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>excess_b_el</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Electricity_Hös</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Hös&lt;-&gt;HS</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>5500703.701841135</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Electricity_Hös</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Pumped_hydro_technology</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Electrolysis</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>4043872.379676969</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Environmental heat</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Heatpump_water</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Fuelcell</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Gas_demand_total</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2171329.883786918</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Gas_storage</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>355584.6298967428</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>GuD</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Material_demand_Gas</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>9275.865990296803</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>excess_b_gas</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Gas_storage</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>337805.3984018926</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>GuD</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>District heating</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>GuD</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>H2_storage</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1689611.309831562</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Heat storage_dist_heat</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>District heating</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>390732.752140057</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Heat storage_seasonal</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Preheater</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1145855.917502219</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Heatpump_air</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>District heating</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>763585.1623259563</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Heatpump_recovery_heat</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>District heating</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Heatpump_water</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>District heating</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Hydro power plant</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>195270.86</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Export_Hydrogen</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Fuelcell</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>H2_storage</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1877345.89981285</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Hydrogen_demand_total</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1390108.146468243</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Methanisation</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1221786.495374172</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PtL</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1244243.147853266</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>excess_b_H2</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Hös&lt;-&gt;HS</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>5500703.701841135</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Hös&lt;-&gt;HS</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Electricity_Hös</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Import_Electricity</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Electricity_Hös</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>5500703.701841135</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Import_Gas</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Import_Hydrogen</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Import_Oil</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Oil_fuel</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Import_Synthetic_fuel</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Oil_fuel</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Import_Wood</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>BioWood</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>6557722.021000034</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Import_solid_fuel</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Biomass</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>3882247.508999479</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Li-Ion_Battery</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Methanisation</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1099607.845836754</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Natrium_Battery</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1533345.754746334</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Netzverluste</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ElectricityOut</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>37419542.98321678</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Oil_fuel</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Material_demand_Oil</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>836815.6246960615</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Oil_fuel</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Oil &amp; fuel_demand_total</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>3455158.953126198</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Oil_fuel</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>excess_b_oil_fuel</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>PV_open_east</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>2588177.221866487</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>PV_open_middle</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>4213199.797083519</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>PV_open_north</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>3255380.519636255</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>PV_open_swest</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>2545999.68166156</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>PV_rooftop_east</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>PV_rooftop_middle</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>PV_rooftop_north</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>PV_rooftop_swest</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Preheater</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Preheater- Electric boiler</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1145855.917502219</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Preheater</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Preheater- WP</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Preheater- Electric boiler</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>District heating</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1146485.185007731</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Preheater- WP</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>District heating</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>PtL</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Oil_fuel</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1097861.601047</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Pumped-Hydro</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Pumped_hydro_storage</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Pumped-Hydro</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Pumped_hydro_technology</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Pumped_hydro_storage</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Pumped-Hydro</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Pumped_hydro_storage_bestand</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>609526.0308260742</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Pumped_hydro_technology</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Electricity_Hös</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Pumped_hydro_technology</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Pumped-Hydro</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Recovery heat</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Heatpump_recovery_heat</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Red-OX_Battery</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>District heating</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Solidfuel</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Biomass_demand_total</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>2012919.487402344</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Solidfuel</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Material_demand_Biomasse</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>100425.4470990297</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>UW</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Environmental heat</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Umgebungsluft</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Umgebungsluftbus</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>587803.1301839355</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Umgebungsluftbus</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Heatpump_air</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>outgoing</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>587803.1301839355</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Wind_east</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>2133986.584684227</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Wind_middle</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>5521819.839000258</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Wind_north</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>7634239.902191051</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Wind_swest</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>ElectricityIn</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>5817151.960510769</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>PV_total</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ElectricityIN</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>12602757.22024782</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Wind_total</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>ElectricityIN</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>incoming</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>21107198.2863863</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>